--- a/inst/sample/SAMPLE-01/spec/listing_figure_spec.xlsx
+++ b/inst/sample/SAMPLE-01/spec/listing_figure_spec.xlsx
@@ -623,7 +623,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -650,6 +650,18 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-14-2-2</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>ADTTE</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/inst/sample/SAMPLE-01/spec/listing_figure_spec.xlsx
+++ b/inst/sample/SAMPLE-01/spec/listing_figure_spec.xlsx
@@ -353,7 +353,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -385,6 +385,16 @@
       <c r="F1" s="1" t="inlineStr">
         <is>
           <t>max_rows</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>blank_row</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>wrap</t>
         </is>
       </c>
     </row>
@@ -427,7 +437,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -453,6 +463,16 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>sep</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>align</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>collapse_repeats</t>
         </is>
       </c>
@@ -500,7 +520,7 @@
           <t>14</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -623,7 +643,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -637,6 +657,11 @@
           <t>datasets</t>
         </is>
       </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>ard</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">

--- a/inst/sample/SAMPLE-01/spec/listing_figure_spec.xlsx
+++ b/inst/sample/SAMPLE-01/spec/listing_figure_spec.xlsx
@@ -416,12 +416,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>AESEV == "SEVERE"</t>
+          <t>AESEV == "SEVERE" &amp; TRTEMFL == "Y"</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>TRT01A | USUBJID | ASTDT</t>
+          <t>TRT01AN | USUBJID | ASTDT</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">

--- a/inst/sample/SAMPLE-01/spec/listing_figure_spec.xlsx
+++ b/inst/sample/SAMPLE-01/spec/listing_figure_spec.xlsx
@@ -13,6 +13,137 @@
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="42">
+  <si>
+    <t>output_id</t>
+  </si>
+  <si>
+    <t>type</t>
+  </si>
+  <si>
+    <t>dataset</t>
+  </si>
+  <si>
+    <t>where</t>
+  </si>
+  <si>
+    <t>sort</t>
+  </si>
+  <si>
+    <t>max_rows</t>
+  </si>
+  <si>
+    <t>blank_row</t>
+  </si>
+  <si>
+    <t>wrap</t>
+  </si>
+  <si>
+    <t>L-16-2-7</t>
+  </si>
+  <si>
+    <t>multiline</t>
+  </si>
+  <si>
+    <t>ADAE</t>
+  </si>
+  <si>
+    <t>AESEV == "SEVERE" &amp; TRTEMFL == "Y"</t>
+  </si>
+  <si>
+    <t>TRT01AN | USUBJID | ASTDT</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>vars</t>
+  </si>
+  <si>
+    <t>label</t>
+  </si>
+  <si>
+    <t>width</t>
+  </si>
+  <si>
+    <t>sep</t>
+  </si>
+  <si>
+    <t>align</t>
+  </si>
+  <si>
+    <t>collapse_repeats</t>
+  </si>
+  <si>
+    <t>TRT01A</t>
+  </si>
+  <si>
+    <t>Treatment</t>
+  </si>
+  <si>
+    <t>USUBJID</t>
+  </si>
+  <si>
+    <t>Subject</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>TRUE</t>
+  </si>
+  <si>
+    <t>AEBODSYS | AEDECOD</t>
+  </si>
+  <si>
+    <t>System Organ Class/\nPreferred Term</t>
+  </si>
+  <si>
+    <t>40</t>
+  </si>
+  <si>
+    <t>ASTDT | AENDT</t>
+  </si>
+  <si>
+    <t>Start/\nEnd</t>
+  </si>
+  <si>
+    <t>AESER</t>
+  </si>
+  <si>
+    <t>Serious</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>AEREL</t>
+  </si>
+  <si>
+    <t>Relation</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>AEOUT</t>
+  </si>
+  <si>
+    <t>Outcome</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>datasets</t>
+  </si>
+  <si>
+    <t>ard</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -356,78 +487,50 @@
   <dimension ref="A1:H2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>output_id</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>type</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>dataset</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>where</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>sort</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>max_rows</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>blank_row</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>wrap</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>L-16-2-7</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>multiline</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>ADAE</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>AESEV == "SEVERE" &amp; TRTEMFL == "Y"</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>TRT01AN | USUBJID | ASTDT</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
+    <row r="1" spans="1:8" s="1" customFormat="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" t="s">
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -440,200 +543,128 @@
   <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>output_id</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>vars</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>label</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>width</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>sep</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>align</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>collapse_repeats</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>L-16-2-7</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>TRT01A</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Treatment</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>L-16-2-7</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>USUBJID</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Subject</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>L-16-2-7</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>AEBODSYS | AEDECOD</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>System Organ Class/\nPreferred Term</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>L-16-2-7</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>ASTDT | AENDT</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Start/\nEnd</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>L-16-2-7</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>AESER</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Serious</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>L-16-2-7</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>AEREL</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Relation</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>L-16-2-7</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>AEOUT</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Outcome</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
+    <row r="1" spans="1:7" s="1" customFormat="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D4" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" t="s">
+        <v>29</v>
+      </c>
+      <c r="C5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D5" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C6" t="s">
+        <v>32</v>
+      </c>
+      <c r="D6" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C7" t="s">
+        <v>35</v>
+      </c>
+      <c r="D7" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" t="s">
+        <v>37</v>
+      </c>
+      <c r="C8" t="s">
+        <v>38</v>
+      </c>
+      <c r="D8" t="s">
+        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -643,48 +674,18 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>output_id</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>datasets</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>ard</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>F-14-2-1</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>ADSL | ADVS</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>F-14-2-2</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>ADTTE</t>
-        </is>
+    <row r="1" spans="1:3" s="1" customFormat="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>41</v>
       </c>
     </row>
   </sheetData>
